--- a/VerveStacks_EST_grids_eur/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST_grids_eur/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST_grids_eur\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01A31FAD-10BD-478A-B77A-59609EF520A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14A6096-3693-43DC-AE68-9A826C066C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="247">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -869,15 +869,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_w34682089-330,e_w34685113-330,e_w768781614-330</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -1368,10 +1359,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4675A54-AFFC-473D-8735-A57000D00B20}">
-  <dimension ref="B2:AJ57"/>
+  <dimension ref="B2:AF57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1384,11 +1375,8 @@
       <c r="U2" t="s">
         <v>163</v>
       </c>
-      <c r="AH2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -1440,17 +1428,8 @@
       <c r="AA3" t="s">
         <v>137</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>120</v>
       </c>
@@ -1517,17 +1496,8 @@
       <c r="AF4" t="s">
         <v>244</v>
       </c>
-      <c r="AH4" t="s">
-        <v>247</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>248</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>121</v>
       </c>
@@ -1591,17 +1561,8 @@
       <c r="AF5" t="s">
         <v>245</v>
       </c>
-      <c r="AH5" t="s">
-        <v>249</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>248</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>122</v>
       </c>
@@ -1666,7 +1627,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>123</v>
       </c>
@@ -1716,7 +1677,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>124</v>
       </c>
@@ -1766,7 +1727,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>125</v>
       </c>
@@ -1816,7 +1777,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>126</v>
       </c>
@@ -1866,7 +1827,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>127</v>
       </c>
@@ -1916,7 +1877,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>128</v>
       </c>
@@ -1966,7 +1927,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -2016,7 +1977,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>130</v>
       </c>
@@ -2066,7 +2027,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>131</v>
       </c>
@@ -2116,7 +2077,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>132</v>
       </c>

--- a/VerveStacks_EST_grids_eur/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST_grids_eur/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST_grids_eur\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14A6096-3693-43DC-AE68-9A826C066C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9171D60-56DB-46E9-A05E-08ED346240B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="246">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -359,9 +359,6 @@
   </si>
   <si>
     <t>Nuclear High</t>
-  </si>
-  <si>
-    <t>USA</t>
   </si>
   <si>
     <t>uc_n</t>
@@ -1367,13 +1364,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="2:32" x14ac:dyDescent="0.45">
@@ -1381,25 +1378,25 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
         <v>117</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>118</v>
-      </c>
-      <c r="E3" t="s">
-        <v>119</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
       </c>
       <c r="I3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" t="s">
         <v>138</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>139</v>
-      </c>
-      <c r="K3" t="s">
-        <v>140</v>
       </c>
       <c r="L3" t="s">
         <v>14</v>
@@ -1408,30 +1405,30 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="U3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V3" t="s">
         <v>3</v>
       </c>
       <c r="W3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4">
         <v>1.106001</v>
@@ -1443,63 +1440,63 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="H4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" t="s">
         <v>141</v>
-      </c>
-      <c r="I4" t="s">
-        <v>142</v>
       </c>
       <c r="J4">
         <v>0.78510837207725603</v>
       </c>
       <c r="K4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q4" t="s">
+        <v>164</v>
+      </c>
+      <c r="R4" t="s">
         <v>165</v>
       </c>
-      <c r="R4" t="s">
+      <c r="U4" t="s">
+        <v>171</v>
+      </c>
+      <c r="V4" t="s">
+        <v>172</v>
+      </c>
+      <c r="W4" t="s">
         <v>166</v>
       </c>
-      <c r="U4" t="s">
-        <v>172</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="X4" t="s">
         <v>173</v>
       </c>
-      <c r="W4" t="s">
-        <v>167</v>
-      </c>
-      <c r="X4" t="s">
-        <v>174</v>
-      </c>
       <c r="AA4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AB4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AC4" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD4" t="s">
         <v>241</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>242</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>243</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5">
         <v>2.212002</v>
@@ -1511,46 +1508,46 @@
         <v>0.99927999999999995</v>
       </c>
       <c r="H5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J5">
         <v>1.9896066262465945E-2</v>
       </c>
       <c r="K5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L5" t="s">
+        <v>141</v>
+      </c>
+      <c r="P5" t="s">
         <v>143</v>
       </c>
-      <c r="L5" t="s">
-        <v>142</v>
-      </c>
-      <c r="P5" t="s">
-        <v>144</v>
-      </c>
       <c r="Q5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R5" t="s">
+        <v>165</v>
+      </c>
+      <c r="U5" t="s">
+        <v>171</v>
+      </c>
+      <c r="V5" t="s">
+        <v>174</v>
+      </c>
+      <c r="W5" t="s">
         <v>166</v>
       </c>
-      <c r="U5" t="s">
-        <v>172</v>
-      </c>
-      <c r="V5" t="s">
-        <v>175</v>
-      </c>
-      <c r="W5" t="s">
-        <v>167</v>
-      </c>
       <c r="X5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -1559,12 +1556,12 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>1.106001</v>
@@ -1576,46 +1573,46 @@
         <v>0.98817999999999995</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J6">
         <v>0.13448608797078096</v>
       </c>
       <c r="K6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R6" t="s">
+        <v>165</v>
+      </c>
+      <c r="U6" t="s">
+        <v>171</v>
+      </c>
+      <c r="V6" t="s">
+        <v>175</v>
+      </c>
+      <c r="W6" t="s">
         <v>166</v>
       </c>
-      <c r="U6" t="s">
-        <v>172</v>
-      </c>
-      <c r="V6" t="s">
-        <v>176</v>
-      </c>
-      <c r="W6" t="s">
-        <v>167</v>
-      </c>
       <c r="X6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -1624,12 +1621,12 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>2.212002</v>
@@ -1641,45 +1638,45 @@
         <v>0.99904000000000004</v>
       </c>
       <c r="H7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J7">
         <v>1.9091364510106474E-2</v>
       </c>
       <c r="K7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R7" t="s">
+        <v>165</v>
+      </c>
+      <c r="U7" t="s">
+        <v>171</v>
+      </c>
+      <c r="V7" t="s">
+        <v>176</v>
+      </c>
+      <c r="W7" t="s">
         <v>166</v>
       </c>
-      <c r="U7" t="s">
-        <v>172</v>
-      </c>
-      <c r="V7" t="s">
-        <v>177</v>
-      </c>
-      <c r="W7" t="s">
-        <v>167</v>
-      </c>
       <c r="X7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8">
         <v>0.49155599999999999</v>
@@ -1691,45 +1688,45 @@
         <v>0.99561999999999995</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J8">
         <v>2.1418109179390448E-2</v>
       </c>
       <c r="K8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R8" t="s">
+        <v>165</v>
+      </c>
+      <c r="U8" t="s">
+        <v>171</v>
+      </c>
+      <c r="V8" t="s">
+        <v>177</v>
+      </c>
+      <c r="W8" t="s">
         <v>166</v>
       </c>
-      <c r="U8" t="s">
-        <v>172</v>
-      </c>
-      <c r="V8" t="s">
-        <v>178</v>
-      </c>
-      <c r="W8" t="s">
-        <v>167</v>
-      </c>
       <c r="X8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9">
         <v>1.106001</v>
@@ -1741,45 +1738,45 @@
         <v>0.99592000000000003</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J9">
         <v>0.78510837207725603</v>
       </c>
       <c r="K9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q9" t="s">
+        <v>164</v>
+      </c>
+      <c r="R9" t="s">
         <v>165</v>
       </c>
-      <c r="R9" t="s">
+      <c r="U9" t="s">
+        <v>171</v>
+      </c>
+      <c r="V9" t="s">
+        <v>178</v>
+      </c>
+      <c r="W9" t="s">
         <v>166</v>
       </c>
-      <c r="U9" t="s">
-        <v>172</v>
-      </c>
-      <c r="V9" t="s">
-        <v>179</v>
-      </c>
-      <c r="W9" t="s">
-        <v>167</v>
-      </c>
       <c r="X9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10">
         <v>1.106001</v>
@@ -1791,45 +1788,45 @@
         <v>0.98992000000000002</v>
       </c>
       <c r="H10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J10">
         <v>1.9896066262465945E-2</v>
       </c>
       <c r="K10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R10" t="s">
+        <v>165</v>
+      </c>
+      <c r="U10" t="s">
+        <v>171</v>
+      </c>
+      <c r="V10" t="s">
+        <v>179</v>
+      </c>
+      <c r="W10" t="s">
         <v>166</v>
       </c>
-      <c r="U10" t="s">
-        <v>172</v>
-      </c>
-      <c r="V10" t="s">
-        <v>180</v>
-      </c>
-      <c r="W10" t="s">
-        <v>167</v>
-      </c>
       <c r="X10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11">
         <v>1.106001</v>
@@ -1841,45 +1838,45 @@
         <v>0.99309999999999998</v>
       </c>
       <c r="H11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J11">
         <v>0.13448608797078096</v>
       </c>
       <c r="K11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R11" t="s">
+        <v>165</v>
+      </c>
+      <c r="U11" t="s">
+        <v>171</v>
+      </c>
+      <c r="V11" t="s">
+        <v>180</v>
+      </c>
+      <c r="W11" t="s">
         <v>166</v>
       </c>
-      <c r="U11" t="s">
-        <v>172</v>
-      </c>
-      <c r="V11" t="s">
-        <v>181</v>
-      </c>
-      <c r="W11" t="s">
-        <v>167</v>
-      </c>
       <c r="X11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12">
         <v>1.106001</v>
@@ -1891,45 +1888,45 @@
         <v>0.99046000000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J12">
         <v>1.9091364510106474E-2</v>
       </c>
       <c r="K12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R12" t="s">
+        <v>165</v>
+      </c>
+      <c r="U12" t="s">
+        <v>171</v>
+      </c>
+      <c r="V12" t="s">
+        <v>181</v>
+      </c>
+      <c r="W12" t="s">
         <v>166</v>
       </c>
-      <c r="U12" t="s">
-        <v>172</v>
-      </c>
-      <c r="V12" t="s">
-        <v>182</v>
-      </c>
-      <c r="W12" t="s">
-        <v>167</v>
-      </c>
       <c r="X12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13">
         <v>1.106001</v>
@@ -1941,45 +1938,45 @@
         <v>0.99658000000000002</v>
       </c>
       <c r="H13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J13">
         <v>2.1418109179390448E-2</v>
       </c>
       <c r="K13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R13" t="s">
+        <v>165</v>
+      </c>
+      <c r="U13" t="s">
+        <v>171</v>
+      </c>
+      <c r="V13" t="s">
+        <v>182</v>
+      </c>
+      <c r="W13" t="s">
         <v>166</v>
       </c>
-      <c r="U13" t="s">
-        <v>172</v>
-      </c>
-      <c r="V13" t="s">
-        <v>183</v>
-      </c>
-      <c r="W13" t="s">
-        <v>167</v>
-      </c>
       <c r="X13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14">
         <v>2.212002</v>
@@ -1991,45 +1988,45 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J14">
         <v>0.78510837207725603</v>
       </c>
       <c r="K14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q14" t="s">
+        <v>164</v>
+      </c>
+      <c r="R14" t="s">
         <v>165</v>
       </c>
-      <c r="R14" t="s">
+      <c r="U14" t="s">
+        <v>171</v>
+      </c>
+      <c r="V14" t="s">
+        <v>183</v>
+      </c>
+      <c r="W14" t="s">
         <v>166</v>
       </c>
-      <c r="U14" t="s">
-        <v>172</v>
-      </c>
-      <c r="V14" t="s">
-        <v>184</v>
-      </c>
-      <c r="W14" t="s">
-        <v>167</v>
-      </c>
       <c r="X14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15">
         <v>1.106001</v>
@@ -2041,45 +2038,45 @@
         <v>0.99351999999999996</v>
       </c>
       <c r="H15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J15">
         <v>1.9896066262465945E-2</v>
       </c>
       <c r="K15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R15" t="s">
+        <v>165</v>
+      </c>
+      <c r="U15" t="s">
+        <v>171</v>
+      </c>
+      <c r="V15" t="s">
+        <v>184</v>
+      </c>
+      <c r="W15" t="s">
         <v>166</v>
       </c>
-      <c r="U15" t="s">
-        <v>172</v>
-      </c>
-      <c r="V15" t="s">
-        <v>185</v>
-      </c>
-      <c r="W15" t="s">
-        <v>167</v>
-      </c>
       <c r="X15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16">
         <v>1.106001</v>
@@ -2091,45 +2088,45 @@
         <v>0.99580000000000002</v>
       </c>
       <c r="H16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J16">
         <v>0.13448608797078096</v>
       </c>
       <c r="K16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R16" t="s">
+        <v>165</v>
+      </c>
+      <c r="U16" t="s">
+        <v>171</v>
+      </c>
+      <c r="V16" t="s">
+        <v>185</v>
+      </c>
+      <c r="W16" t="s">
         <v>166</v>
       </c>
-      <c r="U16" t="s">
-        <v>172</v>
-      </c>
-      <c r="V16" t="s">
-        <v>186</v>
-      </c>
-      <c r="W16" t="s">
-        <v>167</v>
-      </c>
       <c r="X16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17">
         <v>1.106001</v>
@@ -2141,45 +2138,45 @@
         <v>0.98956</v>
       </c>
       <c r="H17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J17">
         <v>1.9091364510106474E-2</v>
       </c>
       <c r="K17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V17" t="s">
+        <v>186</v>
+      </c>
+      <c r="W17" t="s">
         <v>187</v>
       </c>
-      <c r="W17" t="s">
-        <v>188</v>
-      </c>
       <c r="X17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18">
         <v>1.106001</v>
@@ -2191,45 +2188,45 @@
         <v>0.99826000000000004</v>
       </c>
       <c r="H18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J18">
         <v>2.1418109179390448E-2</v>
       </c>
       <c r="K18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="W18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19">
         <v>1.106001</v>
@@ -2241,45 +2238,45 @@
         <v>0.99604000000000004</v>
       </c>
       <c r="H19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J19">
         <v>0.78510837207725603</v>
       </c>
       <c r="K19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q19" t="s">
+        <v>164</v>
+      </c>
+      <c r="R19" t="s">
         <v>165</v>
       </c>
-      <c r="R19" t="s">
-        <v>166</v>
-      </c>
       <c r="U19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20">
         <v>1.106001</v>
@@ -2291,630 +2288,630 @@
         <v>0.99717999999999996</v>
       </c>
       <c r="H20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J20">
         <v>1.9896066262465945E-2</v>
       </c>
       <c r="K20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J21">
         <v>0.13448608797078096</v>
       </c>
       <c r="K21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="W21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J22">
         <v>1.9091364510106474E-2</v>
       </c>
       <c r="K22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="W22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J23">
         <v>2.1418109179390448E-2</v>
       </c>
       <c r="K23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V30" t="s">
+        <v>200</v>
+      </c>
+      <c r="W30" t="s">
         <v>201</v>
       </c>
-      <c r="W30" t="s">
-        <v>202</v>
-      </c>
       <c r="X30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="W31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V33" t="s">
+        <v>204</v>
+      </c>
+      <c r="W33" t="s">
         <v>205</v>
       </c>
-      <c r="W33" t="s">
-        <v>206</v>
-      </c>
       <c r="X33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W35" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="W37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V38" t="s">
+        <v>210</v>
+      </c>
+      <c r="W38" t="s">
         <v>211</v>
       </c>
-      <c r="W38" t="s">
-        <v>212</v>
-      </c>
       <c r="X38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="W41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V42" t="s">
+        <v>215</v>
+      </c>
+      <c r="W42" t="s">
         <v>216</v>
       </c>
-      <c r="W42" t="s">
-        <v>217</v>
-      </c>
       <c r="X42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="W43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="W44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="W45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V46" t="s">
+        <v>220</v>
+      </c>
+      <c r="W46" t="s">
         <v>221</v>
       </c>
-      <c r="W46" t="s">
-        <v>222</v>
-      </c>
       <c r="X46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="W47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V48" t="s">
+        <v>223</v>
+      </c>
+      <c r="W48" t="s">
         <v>224</v>
       </c>
-      <c r="W48" t="s">
-        <v>225</v>
-      </c>
       <c r="X48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V50" t="s">
+        <v>226</v>
+      </c>
+      <c r="W50" t="s">
         <v>227</v>
       </c>
-      <c r="W50" t="s">
-        <v>228</v>
-      </c>
       <c r="X50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V51" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="X51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V52" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V53" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U54" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V54" t="s">
+        <v>231</v>
+      </c>
+      <c r="W54" t="s">
         <v>232</v>
       </c>
-      <c r="W54" t="s">
-        <v>233</v>
-      </c>
       <c r="X54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W55" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="X55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V56" t="s">
+        <v>234</v>
+      </c>
+      <c r="W56" t="s">
         <v>235</v>
       </c>
-      <c r="W56" t="s">
-        <v>236</v>
-      </c>
       <c r="X56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2929,42 +2926,42 @@
   <sheetData>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
         <v>92</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>93</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>94</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>95</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>96</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>97</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>98</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>99</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>100</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>101</v>
-      </c>
-      <c r="L10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -2972,34 +2969,34 @@
         <v>2030</v>
       </c>
       <c r="C11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" t="s">
         <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
       </c>
       <c r="E11">
         <v>0.36699999999999999</v>
       </c>
       <c r="F11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" t="s">
         <v>105</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>106</v>
-      </c>
-      <c r="H11" t="s">
-        <v>107</v>
       </c>
       <c r="I11" s="12">
         <v>45155</v>
       </c>
       <c r="J11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="L11" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3007,34 +3004,34 @@
         <v>2030</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="F12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" t="s">
         <v>105</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>106</v>
-      </c>
-      <c r="H12" t="s">
-        <v>107</v>
       </c>
       <c r="I12" s="12">
         <v>45155</v>
       </c>
       <c r="J12" t="s">
+        <v>107</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="L12" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3042,34 +3039,34 @@
         <v>2030</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" t="s">
         <v>105</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>106</v>
-      </c>
-      <c r="H13" t="s">
-        <v>107</v>
       </c>
       <c r="I13" s="12">
         <v>45155</v>
       </c>
       <c r="J13" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="L13" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3077,34 +3074,34 @@
         <v>2030</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>1.31</v>
       </c>
       <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" t="s">
         <v>105</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>106</v>
-      </c>
-      <c r="H14" t="s">
-        <v>107</v>
       </c>
       <c r="I14" s="12">
         <v>45155</v>
       </c>
       <c r="J14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K14" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="L14" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3112,34 +3109,34 @@
         <v>2030</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E15">
         <v>1.2</v>
       </c>
       <c r="F15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" t="s">
         <v>105</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>106</v>
-      </c>
-      <c r="H15" t="s">
-        <v>107</v>
       </c>
       <c r="I15" s="12">
         <v>45155</v>
       </c>
       <c r="J15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="L15" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3147,34 +3144,34 @@
         <v>2030</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E16">
         <v>1.54</v>
       </c>
       <c r="F16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" t="s">
         <v>105</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>106</v>
-      </c>
-      <c r="H16" t="s">
-        <v>107</v>
       </c>
       <c r="I16" s="12">
         <v>45155</v>
       </c>
       <c r="J16" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="L16" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3182,34 +3179,34 @@
         <v>2030</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
         <v>105</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>106</v>
-      </c>
-      <c r="H17" t="s">
-        <v>107</v>
       </c>
       <c r="I17" s="12">
         <v>45155</v>
       </c>
       <c r="J17" t="s">
+        <v>107</v>
+      </c>
+      <c r="K17" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="L17" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3217,34 +3214,34 @@
         <v>2030</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>3.7149999999999999</v>
       </c>
       <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
         <v>105</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>106</v>
-      </c>
-      <c r="H18" t="s">
-        <v>107</v>
       </c>
       <c r="I18" s="12">
         <v>45155</v>
       </c>
       <c r="J18" t="s">
+        <v>107</v>
+      </c>
+      <c r="K18" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="L18" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3252,34 +3249,34 @@
         <v>2030</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E19">
         <v>3.1240000000000001</v>
       </c>
       <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" t="s">
         <v>105</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>106</v>
-      </c>
-      <c r="H19" t="s">
-        <v>107</v>
       </c>
       <c r="I19" s="12">
         <v>45155</v>
       </c>
       <c r="J19" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="L19" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3287,34 +3284,34 @@
         <v>2030</v>
       </c>
       <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
         <v>114</v>
-      </c>
-      <c r="D20" t="s">
-        <v>115</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" t="s">
         <v>105</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>106</v>
-      </c>
-      <c r="H20" t="s">
-        <v>107</v>
       </c>
       <c r="I20" s="12">
         <v>45155</v>
       </c>
       <c r="J20" t="s">
+        <v>107</v>
+      </c>
+      <c r="K20" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="L20" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3322,34 +3319,34 @@
         <v>2030</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E21">
         <v>16.376000000000001</v>
       </c>
       <c r="F21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" t="s">
         <v>105</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>106</v>
-      </c>
-      <c r="H21" t="s">
-        <v>107</v>
       </c>
       <c r="I21" s="12">
         <v>45155</v>
       </c>
       <c r="J21" t="s">
+        <v>107</v>
+      </c>
+      <c r="K21" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="L21" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3357,34 +3354,34 @@
         <v>2030</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E22">
         <v>0.26600000000000001</v>
       </c>
       <c r="F22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" t="s">
         <v>105</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>106</v>
-      </c>
-      <c r="H22" t="s">
-        <v>107</v>
       </c>
       <c r="I22" s="12">
         <v>45155</v>
       </c>
       <c r="J22" t="s">
+        <v>107</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="L22" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3392,34 +3389,34 @@
         <v>2030</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23">
         <v>39.503999999999998</v>
       </c>
       <c r="F23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" t="s">
         <v>105</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>106</v>
-      </c>
-      <c r="H23" t="s">
-        <v>107</v>
       </c>
       <c r="I23" s="12">
         <v>45155</v>
       </c>
       <c r="J23" t="s">
+        <v>107</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="L23" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3427,34 +3424,34 @@
         <v>2030</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24">
         <v>33.22</v>
       </c>
       <c r="F24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
         <v>105</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>106</v>
-      </c>
-      <c r="H24" t="s">
-        <v>107</v>
       </c>
       <c r="I24" s="12">
         <v>45155</v>
       </c>
       <c r="J24" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="L24" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -3462,34 +3459,34 @@
         <v>2030</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E25">
         <v>10.634</v>
       </c>
       <c r="F25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" t="s">
         <v>105</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>106</v>
-      </c>
-      <c r="H25" t="s">
-        <v>107</v>
       </c>
       <c r="I25" s="12">
         <v>45155</v>
       </c>
       <c r="J25" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="L25" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3608,7 +3605,7 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
@@ -3631,7 +3628,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -3664,7 +3661,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -3877,7 +3874,7 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3">
         <v>0.11415525114155252</v>
@@ -3903,7 +3900,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -3979,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -4201,7 +4198,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -4262,31 +4259,31 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0.5</v>
       </c>
-      <c r="H11">
-        <v>1.5</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
@@ -4296,7 +4293,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -4304,16 +4301,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -4338,18 +4335,18 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -4368,18 +4365,18 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -4398,18 +4395,18 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
         <f>G11</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <f>H11</f>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -4428,18 +4425,18 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
         <f>I11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -9143,7 +9140,7 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B346">
         <v>2000</v>
@@ -9269,7 +9266,7 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B355">
         <v>2001</v>
@@ -9395,7 +9392,7 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B364">
         <v>2002</v>
@@ -9521,7 +9518,7 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B373">
         <v>2003</v>
@@ -9647,7 +9644,7 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B382">
         <v>2004</v>
@@ -9773,7 +9770,7 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B391">
         <v>2005</v>
@@ -9899,7 +9896,7 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B400">
         <v>2006</v>
@@ -10025,7 +10022,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B409">
         <v>2007</v>
@@ -10151,7 +10148,7 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B418">
         <v>2008</v>
@@ -10277,7 +10274,7 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B427">
         <v>2009</v>
@@ -10403,7 +10400,7 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B436">
         <v>2010</v>
@@ -10529,7 +10526,7 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B445">
         <v>2011</v>
@@ -10655,7 +10652,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B454">
         <v>2012</v>
@@ -10781,7 +10778,7 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B463">
         <v>2013</v>
@@ -10907,7 +10904,7 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B472">
         <v>2014</v>
@@ -11033,7 +11030,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B481">
         <v>2015</v>
@@ -11159,7 +11156,7 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B490">
         <v>2016</v>
@@ -11285,7 +11282,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B499">
         <v>2017</v>
@@ -11411,7 +11408,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B508">
         <v>2018</v>
@@ -11537,7 +11534,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B517">
         <v>2019</v>
@@ -11663,7 +11660,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B526">
         <v>2020</v>
@@ -11789,7 +11786,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B535">
         <v>2021</v>
@@ -11915,7 +11912,7 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B544">
         <v>2022</v>
@@ -12041,7 +12038,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B553">
         <v>2023</v>
@@ -12475,7 +12472,7 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B584">
         <v>2018</v>
@@ -12489,7 +12486,7 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B585">
         <v>2019</v>
@@ -12503,7 +12500,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B586">
         <v>2020</v>
@@ -12517,7 +12514,7 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B587">
         <v>2021</v>
@@ -12531,7 +12528,7 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B588">
         <v>2022</v>
@@ -12545,7 +12542,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B589">
         <v>2023</v>
@@ -12559,7 +12556,7 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B590">
         <v>2024</v>
@@ -12573,7 +12570,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B591">
         <v>2011</v>
@@ -12587,7 +12584,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B592">
         <v>2012</v>
@@ -12601,7 +12598,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B593">
         <v>2013</v>
@@ -12615,7 +12612,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B594">
         <v>2014</v>
@@ -12629,7 +12626,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B595">
         <v>2015</v>
@@ -12643,7 +12640,7 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B596">
         <v>2016</v>
@@ -12657,7 +12654,7 @@
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B597">
         <v>2017</v>
@@ -12671,7 +12668,7 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B598">
         <v>2004</v>
@@ -12685,7 +12682,7 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B599">
         <v>2005</v>
@@ -12699,7 +12696,7 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B600">
         <v>2006</v>
@@ -12713,7 +12710,7 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B601">
         <v>2007</v>
@@ -12727,7 +12724,7 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B602">
         <v>2008</v>
@@ -12741,7 +12738,7 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B603">
         <v>2009</v>
@@ -12755,7 +12752,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B604">
         <v>2010</v>
@@ -12769,7 +12766,7 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B605">
         <v>2002</v>
@@ -12783,7 +12780,7 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B606">
         <v>2003</v>
@@ -12797,7 +12794,7 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B607">
         <v>2002</v>
@@ -12811,7 +12808,7 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B608">
         <v>2003</v>
@@ -12825,7 +12822,7 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B609">
         <v>2004</v>
@@ -12839,7 +12836,7 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B610">
         <v>2005</v>
@@ -12853,7 +12850,7 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B611">
         <v>2006</v>
@@ -12867,7 +12864,7 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B612">
         <v>2007</v>
@@ -12881,7 +12878,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B613">
         <v>2008</v>
@@ -12895,7 +12892,7 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B614">
         <v>2009</v>
@@ -12909,7 +12906,7 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B615">
         <v>2010</v>
@@ -12923,7 +12920,7 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B616">
         <v>2011</v>
@@ -12937,7 +12934,7 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B617">
         <v>2012</v>
@@ -12951,7 +12948,7 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B618">
         <v>2013</v>
@@ -12965,7 +12962,7 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B619">
         <v>2014</v>
@@ -12979,7 +12976,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B620">
         <v>2015</v>
@@ -12993,7 +12990,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B621">
         <v>2016</v>
@@ -13007,7 +13004,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2017</v>
@@ -13021,7 +13018,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B623">
         <v>2018</v>
@@ -13035,7 +13032,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B624">
         <v>2019</v>
@@ -13049,7 +13046,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B625">
         <v>2020</v>
@@ -13063,7 +13060,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B626">
         <v>2021</v>
@@ -13077,7 +13074,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B627">
         <v>2022</v>

--- a/VerveStacks_EST_grids_eur/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EST_grids_eur/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST_grids_eur\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9171D60-56DB-46E9-A05E-08ED346240B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE8A57E-DCAA-4945-874C-60B5487304E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4262,16 +4262,18 @@
         <v>171</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <f>C11*3</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <f>E11*4</f>
+        <v>0.4</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -4342,11 +4344,11 @@
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>2</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -4372,11 +4374,11 @@
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H21">
         <v>4</v>
